--- a/outputs/monitor_xlsx/20260410.xlsx
+++ b/outputs/monitor_xlsx/20260410.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,7 +1250,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>80.75</v>
       </c>
       <c r="E4" s="6" t="n">
@@ -1264,7 +1263,10 @@
         <v>59383</v>
       </c>
       <c r="H4" t="n">
-        <v>93888</v>
+        <v>153271</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>4474</v>
@@ -1276,11 +1278,14 @@
         <v>9581</v>
       </c>
       <c r="M4" t="n">
-        <v>47927</v>
+        <v>57508</v>
       </c>
       <c r="N4" t="n">
         <v>-4628631</v>
       </c>
+      <c r="O4" t="n">
+        <v>6.24</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1303,7 +1308,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>814</v>
       </c>
       <c r="E5" s="6" t="n">
@@ -1316,13 +1321,13 @@
         <v>-119</v>
       </c>
       <c r="H5" t="n">
-        <v>-547</v>
+        <v>-667</v>
       </c>
       <c r="I5" t="n">
         <v>-53</v>
       </c>
       <c r="J5" t="n">
-        <v>-129</v>
+        <v>-182</v>
       </c>
       <c r="K5" t="n">
         <v>23</v>
@@ -1331,11 +1336,14 @@
         <v>2697</v>
       </c>
       <c r="M5" t="n">
-        <v>10701</v>
+        <v>13398</v>
       </c>
       <c r="N5" t="n">
         <v>-78970</v>
       </c>
+      <c r="O5" t="n">
+        <v>-6.23</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1358,7 +1366,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1735</v>
       </c>
       <c r="E6" s="6" t="n">
@@ -1371,13 +1379,13 @@
         <v>581</v>
       </c>
       <c r="H6" t="n">
-        <v>6393</v>
+        <v>6974</v>
       </c>
       <c r="I6" t="n">
         <v>25</v>
       </c>
       <c r="J6" t="n">
-        <v>-49</v>
+        <v>-24</v>
       </c>
       <c r="K6" t="n">
         <v>258</v>
@@ -1386,11 +1394,14 @@
         <v>4858</v>
       </c>
       <c r="M6" t="n">
-        <v>20920</v>
+        <v>25778</v>
       </c>
       <c r="N6" t="n">
         <v>-649282</v>
       </c>
+      <c r="O6" t="n">
+        <v>16.91</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1413,7 +1424,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>2000</v>
       </c>
       <c r="E7" s="6" t="n">
@@ -1426,13 +1437,13 @@
         <v>8160</v>
       </c>
       <c r="H7" t="n">
-        <v>15610</v>
+        <v>23770</v>
       </c>
       <c r="I7" t="n">
         <v>-175</v>
       </c>
       <c r="J7" t="n">
-        <v>576</v>
+        <v>401</v>
       </c>
       <c r="K7" t="n">
         <v>526</v>
@@ -1441,11 +1452,14 @@
         <v>27217</v>
       </c>
       <c r="M7" t="n">
-        <v>106031</v>
+        <v>133248</v>
       </c>
       <c r="N7" t="n">
         <v>-6483071</v>
       </c>
+      <c r="O7" t="n">
+        <v>7.66</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1468,7 +1482,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1835</v>
       </c>
       <c r="E8" s="6" t="n">
@@ -1481,13 +1495,13 @@
         <v>692</v>
       </c>
       <c r="H8" t="n">
-        <v>-2258</v>
+        <v>-1566</v>
       </c>
       <c r="I8" t="n">
         <v>227</v>
       </c>
       <c r="J8" t="n">
-        <v>772</v>
+        <v>998</v>
       </c>
       <c r="K8" t="n">
         <v>36</v>
@@ -1496,11 +1510,14 @@
         <v>1653</v>
       </c>
       <c r="M8" t="n">
-        <v>7307</v>
+        <v>8960</v>
       </c>
       <c r="N8" t="n">
         <v>-140257</v>
       </c>
+      <c r="O8" t="n">
+        <v>14.94</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1523,7 +1540,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1785</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -1536,13 +1553,13 @@
         <v>-967</v>
       </c>
       <c r="H9" t="n">
-        <v>-159</v>
+        <v>-1126</v>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="K9" t="n">
         <v>95</v>
@@ -1551,11 +1568,14 @@
         <v>1829</v>
       </c>
       <c r="M9" t="n">
-        <v>8283</v>
+        <v>10112</v>
       </c>
       <c r="N9" t="n">
         <v>-106304</v>
       </c>
+      <c r="O9" t="n">
+        <v>12.53</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1578,7 +1598,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>3420</v>
       </c>
       <c r="E10" s="6" t="n">
@@ -1591,13 +1611,13 @@
         <v>-195</v>
       </c>
       <c r="H10" t="n">
-        <v>679</v>
+        <v>485</v>
       </c>
       <c r="I10" t="n">
         <v>110</v>
       </c>
       <c r="J10" t="n">
-        <v>372</v>
+        <v>482</v>
       </c>
       <c r="K10" t="n">
         <v>142</v>
@@ -1606,11 +1626,14 @@
         <v>1824</v>
       </c>
       <c r="M10" t="n">
-        <v>7526</v>
+        <v>9350</v>
       </c>
       <c r="N10" t="n">
         <v>-89520</v>
       </c>
+      <c r="O10" t="n">
+        <v>20.22</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1633,7 +1656,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2325</v>
       </c>
       <c r="E11" s="6" t="n">
@@ -1646,13 +1669,13 @@
         <v>543</v>
       </c>
       <c r="H11" t="n">
-        <v>-73</v>
+        <v>471</v>
       </c>
       <c r="I11" t="n">
         <v>-10</v>
       </c>
       <c r="J11" t="n">
-        <v>-17</v>
+        <v>-27</v>
       </c>
       <c r="K11" t="n">
         <v>77</v>
@@ -1661,11 +1684,14 @@
         <v>3825</v>
       </c>
       <c r="M11" t="n">
-        <v>15378</v>
+        <v>19203</v>
       </c>
       <c r="N11" t="n">
         <v>-19386</v>
       </c>
+      <c r="O11" t="n">
+        <v>17.81</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1688,7 +1714,7 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>7930</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -1701,13 +1727,13 @@
         <v>-9</v>
       </c>
       <c r="H12" t="n">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="I12" t="n">
         <v>-21</v>
       </c>
       <c r="J12" t="n">
-        <v>-189</v>
+        <v>-210</v>
       </c>
       <c r="K12" t="n">
         <v>14</v>
@@ -1716,11 +1742,14 @@
         <v>324</v>
       </c>
       <c r="M12" t="n">
-        <v>1319</v>
+        <v>1643</v>
       </c>
       <c r="N12" t="n">
         <v>-9010</v>
       </c>
+      <c r="O12" t="n">
+        <v>7.24</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1743,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
+        <v>2.16</v>
       </c>
       <c r="F13" t="n">
-        <v>2730</v>
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>261</v>
       </c>
       <c r="H13" t="n">
-        <v>-180</v>
+        <v>81</v>
       </c>
       <c r="I13" t="n">
         <v>-38</v>
       </c>
       <c r="J13" t="n">
-        <v>516</v>
+        <v>478</v>
       </c>
       <c r="K13" t="n">
         <v>-18</v>
@@ -1771,11 +1800,14 @@
         <v>78</v>
       </c>
       <c r="M13" t="n">
-        <v>205</v>
+        <v>283</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1798,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
+        <v>9.94</v>
       </c>
       <c r="F14" t="n">
-        <v>3871</v>
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>99</v>
       </c>
       <c r="H14" t="n">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="I14" t="n">
         <v>-430</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-430</v>
       </c>
       <c r="K14" t="n">
         <v>46</v>
@@ -1826,11 +1858,14 @@
         <v>-238</v>
       </c>
       <c r="M14" t="n">
-        <v>-565</v>
+        <v>-803</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1853,20 +1888,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
       </c>
       <c r="F15" t="n">
-        <v>1350</v>
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>166</v>
       </c>
       <c r="H15" t="n">
-        <v>-299</v>
+        <v>-134</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
@@ -1878,11 +1916,14 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-195</v>
+        <v>-194</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1905,20 +1946,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F16" t="n">
-        <v>904</v>
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-26</v>
       </c>
       <c r="H16" t="n">
-        <v>108</v>
+        <v>82</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>55</v>
@@ -1930,11 +1974,14 @@
         <v>95</v>
       </c>
       <c r="M16" t="n">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1952,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>633</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>9.9</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1083</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>1035</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-1</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>1673</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>14</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>9636</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>48928</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-21510</v>
       </c>
-      <c r="N17" t="n">
-        <v>58.15</v>
+      <c r="O17" t="n">
+        <v>56.83</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260410.xlsx
+++ b/outputs/monitor_xlsx/20260410.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>56.83</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1575</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5738</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-1441</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-3904</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-276</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1223</v>
+      </c>
+      <c r="K18" t="n">
+        <v>91</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6375</v>
+      </c>
+      <c r="M18" t="n">
+        <v>32156</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400967</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>638</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31035</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>3245</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5168</v>
+      </c>
+      <c r="I19" t="n">
+        <v>509</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6090</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1345</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34160</v>
+      </c>
+      <c r="M19" t="n">
+        <v>173786</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393545</v>
+      </c>
+      <c r="O19" t="n">
+        <v>19.71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>667</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>20854</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-2365</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3180</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1227</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5715</v>
+      </c>
+      <c r="K20" t="n">
+        <v>579</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8104</v>
+      </c>
+      <c r="M20" t="n">
+        <v>41766</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-160956</v>
+      </c>
+      <c r="O20" t="n">
+        <v>18.07</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
